--- a/outputs/daily/predictions_2026-07-09.xlsx
+++ b/outputs/daily/predictions_2026-07-09.xlsx
@@ -924,31 +924,31 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.74925694555776</v>
+        <v>1.733775811587928</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8925600569467425</v>
+        <v>0.8860411909165746</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6077525012526667</v>
+        <v>0.6047260627741885</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2432645020153732</v>
+        <v>0.2468839320974151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1489829967319602</v>
+        <v>0.1483900051283964</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4866134533168868</v>
+        <v>0.4768490780095746</v>
       </c>
       <c r="T2" t="n">
-        <v>1.826220309658736</v>
+        <v>1.79807279334995</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7937796903412643</v>
+        <v>0.7819272066500501</v>
       </c>
       <c r="V2" t="n">
         <v>0.6052086943130369</v>
@@ -966,25 +966,25 @@
         <v>0.454993923791467</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5650589423056775</v>
+        <v>0.5629943598841274</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2564149467006178</v>
+        <v>0.2580904191631661</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1785261109937047</v>
+        <v>0.1789152209527065</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4920157641212688</v>
+        <v>0.4865327943016178</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5079842358787312</v>
+        <v>0.5134672056983822</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4988441231396118</v>
+        <v>0.4951010193677622</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5011558768603882</v>
+        <v>0.5048989806322378</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -992,22 +992,22 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.74938</v>
+        <v>1.73378</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.89313</v>
+        <v>0.887595</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.64251</v>
+        <v>2.621375</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.596188779087049</v>
+        <v>0.5944620580902702</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.2213518667297095</v>
+        <v>0.2232185068781633</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1824593541832415</v>
+        <v>0.1823194350315664</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.596188779087049</v>
+        <v>0.5944620580902702</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4894</v>
+        <v>0.4865</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5135</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5135</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.729</v>
+        <v>0.7284</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.271</v>
+        <v>0.2716</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.729</v>
+        <v>0.7284</v>
       </c>
       <c r="BF2" t="n">
         <v>0.6</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>6.712175361857772</v>
+        <v>6.73899835190879</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1824593541832415</v>
+        <v>0.1823194350315664</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.03347635745128136</v>
+        <v>0.03392942990317008</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2246991816892345</v>
+        <v>0.2286503721986679</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>6.712175361857772</v>
+        <v>6.73899835190879</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1824593541832415</v>
+        <v>0.1823194350315664</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.03347635745128136</v>
+        <v>0.03392942990317008</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.2246991816892345</v>
+        <v>0.2286503721986679</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.1223371142808909</v>
+        <v>0.1230462618247359</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.1134813294989433</v>
+        <v>0.1150611971726274</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.1089812313110932</v>
+        <v>0.1094421890032182</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.09727229402515546</v>
+        <v>0.09697028748092824</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.08235344985396539</v>
+        <v>0.08400237072039436</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.06354539193545555</v>
+        <v>0.06324940668700466</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>0.05671807864461327</v>
+        <v>0.05604157962572037</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.05245718753049396</v>
+        <v>0.0533322589392995</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.04963328258602371</v>
+        <v>0.04955638925682802</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.04341068214721652</v>
+        <v>0.04295983450156214</v>
       </c>
     </row>
   </sheetData>
